--- a/data_lake/fixed_income/South Korea/KOFR.xlsx
+++ b/data_lake/fixed_income/South Korea/KOFR.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10713"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10821"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tommy/Desktop/Pycharm/FinancialData/data_lake/fixed_income/South Korea/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/junghunlee/Desktop/Pycharm/FinancialData/data_lake/fixed_income/South Korea/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76949A6F-7821-6A45-A358-D9EE53279D24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E8FA26F-72CD-334E-B8A7-E88E20E836B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25640" yWindow="600" windowWidth="25560" windowHeight="20260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="18100" yWindow="780" windowWidth="17900" windowHeight="20940" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="KOFR" sheetId="2" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2133" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2155" uniqueCount="11">
   <si>
     <t>KOFR</t>
   </si>
@@ -259,10 +259,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>KOFR!$A$2:$A$2067</c:f>
+              <c:f>KOFR!$A$2:$A$12067</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd;@</c:formatCode>
-                <c:ptCount val="2066"/>
+                <c:ptCount val="12066"/>
                 <c:pt idx="0">
                   <c:v>43102</c:v>
                 </c:pt>
@@ -6460,16 +6460,253 @@
                 </c:pt>
                 <c:pt idx="2065">
                   <c:v>46164</c:v>
+                </c:pt>
+                <c:pt idx="2066">
+                  <c:v>46168</c:v>
+                </c:pt>
+                <c:pt idx="2067">
+                  <c:v>46169</c:v>
+                </c:pt>
+                <c:pt idx="2068">
+                  <c:v>46170</c:v>
+                </c:pt>
+                <c:pt idx="2069">
+                  <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="2070">
+                  <c:v>46174</c:v>
+                </c:pt>
+                <c:pt idx="2071">
+                  <c:v>46175</c:v>
+                </c:pt>
+                <c:pt idx="2072">
+                  <c:v>46177</c:v>
+                </c:pt>
+                <c:pt idx="2073">
+                  <c:v>46178</c:v>
+                </c:pt>
+                <c:pt idx="2074">
+                  <c:v>46181</c:v>
+                </c:pt>
+                <c:pt idx="2075">
+                  <c:v>46182</c:v>
+                </c:pt>
+                <c:pt idx="2076">
+                  <c:v>46183</c:v>
+                </c:pt>
+                <c:pt idx="2077">
+                  <c:v>46184</c:v>
+                </c:pt>
+                <c:pt idx="2078">
+                  <c:v>46185</c:v>
+                </c:pt>
+                <c:pt idx="2079">
+                  <c:v>46188</c:v>
+                </c:pt>
+                <c:pt idx="2080">
+                  <c:v>46189</c:v>
+                </c:pt>
+                <c:pt idx="2081">
+                  <c:v>46190</c:v>
+                </c:pt>
+                <c:pt idx="2082">
+                  <c:v>46191</c:v>
+                </c:pt>
+                <c:pt idx="2083">
+                  <c:v>46192</c:v>
+                </c:pt>
+                <c:pt idx="2084">
+                  <c:v>46195</c:v>
+                </c:pt>
+                <c:pt idx="2085">
+                  <c:v>46196</c:v>
+                </c:pt>
+                <c:pt idx="2086">
+                  <c:v>46197</c:v>
+                </c:pt>
+                <c:pt idx="2087">
+                  <c:v>46198</c:v>
+                </c:pt>
+                <c:pt idx="2088">
+                  <c:v>46199</c:v>
+                </c:pt>
+                <c:pt idx="2089">
+                  <c:v>46202</c:v>
+                </c:pt>
+                <c:pt idx="2090">
+                  <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="2091">
+                  <c:v>46204</c:v>
+                </c:pt>
+                <c:pt idx="2092">
+                  <c:v>46205</c:v>
+                </c:pt>
+                <c:pt idx="2093">
+                  <c:v>46206</c:v>
+                </c:pt>
+                <c:pt idx="2094">
+                  <c:v>46209</c:v>
+                </c:pt>
+                <c:pt idx="2095">
+                  <c:v>46210</c:v>
+                </c:pt>
+                <c:pt idx="2096">
+                  <c:v>46211</c:v>
+                </c:pt>
+                <c:pt idx="2097">
+                  <c:v>46212</c:v>
+                </c:pt>
+                <c:pt idx="2098">
+                  <c:v>46213</c:v>
+                </c:pt>
+                <c:pt idx="2099">
+                  <c:v>46216</c:v>
+                </c:pt>
+                <c:pt idx="2100">
+                  <c:v>46217</c:v>
+                </c:pt>
+                <c:pt idx="2101">
+                  <c:v>46218</c:v>
+                </c:pt>
+                <c:pt idx="2102">
+                  <c:v>46219</c:v>
+                </c:pt>
+                <c:pt idx="2103">
+                  <c:v>46223</c:v>
+                </c:pt>
+                <c:pt idx="2104">
+                  <c:v>46224</c:v>
+                </c:pt>
+                <c:pt idx="2105">
+                  <c:v>46225</c:v>
+                </c:pt>
+                <c:pt idx="2106">
+                  <c:v>46226</c:v>
+                </c:pt>
+                <c:pt idx="2107">
+                  <c:v>46227</c:v>
+                </c:pt>
+                <c:pt idx="2108">
+                  <c:v>46230</c:v>
+                </c:pt>
+                <c:pt idx="2109">
+                  <c:v>46231</c:v>
+                </c:pt>
+                <c:pt idx="2110">
+                  <c:v>46232</c:v>
+                </c:pt>
+                <c:pt idx="2111">
+                  <c:v>46233</c:v>
+                </c:pt>
+                <c:pt idx="2112">
+                  <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="2113">
+                  <c:v>46237</c:v>
+                </c:pt>
+                <c:pt idx="2114">
+                  <c:v>46238</c:v>
+                </c:pt>
+                <c:pt idx="2115">
+                  <c:v>46239</c:v>
+                </c:pt>
+                <c:pt idx="2116">
+                  <c:v>46240</c:v>
+                </c:pt>
+                <c:pt idx="2117">
+                  <c:v>46241</c:v>
+                </c:pt>
+                <c:pt idx="2118">
+                  <c:v>46244</c:v>
+                </c:pt>
+                <c:pt idx="2119">
+                  <c:v>46245</c:v>
+                </c:pt>
+                <c:pt idx="2120">
+                  <c:v>46246</c:v>
+                </c:pt>
+                <c:pt idx="2121">
+                  <c:v>46247</c:v>
+                </c:pt>
+                <c:pt idx="2122">
+                  <c:v>46248</c:v>
+                </c:pt>
+                <c:pt idx="2123">
+                  <c:v>46252</c:v>
+                </c:pt>
+                <c:pt idx="2124">
+                  <c:v>46253</c:v>
+                </c:pt>
+                <c:pt idx="2125">
+                  <c:v>46254</c:v>
+                </c:pt>
+                <c:pt idx="2126">
+                  <c:v>46255</c:v>
+                </c:pt>
+                <c:pt idx="2127">
+                  <c:v>46258</c:v>
+                </c:pt>
+                <c:pt idx="2128">
+                  <c:v>46259</c:v>
+                </c:pt>
+                <c:pt idx="2129">
+                  <c:v>46260</c:v>
+                </c:pt>
+                <c:pt idx="2130">
+                  <c:v>46261</c:v>
+                </c:pt>
+                <c:pt idx="2131">
+                  <c:v>46262</c:v>
+                </c:pt>
+                <c:pt idx="2132">
+                  <c:v>46265</c:v>
+                </c:pt>
+                <c:pt idx="2133">
+                  <c:v>46266</c:v>
+                </c:pt>
+                <c:pt idx="2134">
+                  <c:v>46267</c:v>
+                </c:pt>
+                <c:pt idx="2135">
+                  <c:v>46268</c:v>
+                </c:pt>
+                <c:pt idx="2136">
+                  <c:v>46269</c:v>
+                </c:pt>
+                <c:pt idx="2137">
+                  <c:v>46272</c:v>
+                </c:pt>
+                <c:pt idx="2138">
+                  <c:v>46273</c:v>
+                </c:pt>
+                <c:pt idx="2139">
+                  <c:v>46274</c:v>
+                </c:pt>
+                <c:pt idx="2140">
+                  <c:v>46275</c:v>
+                </c:pt>
+                <c:pt idx="2141">
+                  <c:v>46276</c:v>
+                </c:pt>
+                <c:pt idx="2142">
+                  <c:v>46279</c:v>
+                </c:pt>
+                <c:pt idx="2143">
+                  <c:v>46280</c:v>
+                </c:pt>
+                <c:pt idx="2144">
+                  <c:v>46281</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>KOFR!$E$2:$E$2067</c:f>
+              <c:f>KOFR!$E$2:$E$12067</c:f>
               <c:numCache>
                 <c:formatCode>_(* #,##0.000_);_(* \(#,##0.000\);_(* "-"??_);_(@_)</c:formatCode>
-                <c:ptCount val="2066"/>
+                <c:ptCount val="12066"/>
                 <c:pt idx="0">
                   <c:v>1.649</c:v>
                 </c:pt>
@@ -12667,6 +12904,243 @@
                 </c:pt>
                 <c:pt idx="2065">
                   <c:v>2.5299999999999998</c:v>
+                </c:pt>
+                <c:pt idx="2066">
+                  <c:v>2.54</c:v>
+                </c:pt>
+                <c:pt idx="2067">
+                  <c:v>2.5499999999999998</c:v>
+                </c:pt>
+                <c:pt idx="2068">
+                  <c:v>2.5379999999999998</c:v>
+                </c:pt>
+                <c:pt idx="2069">
+                  <c:v>2.56</c:v>
+                </c:pt>
+                <c:pt idx="2070">
+                  <c:v>2.5390000000000001</c:v>
+                </c:pt>
+                <c:pt idx="2071">
+                  <c:v>2.5289999999999999</c:v>
+                </c:pt>
+                <c:pt idx="2072">
+                  <c:v>2.5190000000000001</c:v>
+                </c:pt>
+                <c:pt idx="2073">
+                  <c:v>2.5089999999999999</c:v>
+                </c:pt>
+                <c:pt idx="2074">
+                  <c:v>2.5099999999999998</c:v>
+                </c:pt>
+                <c:pt idx="2075">
+                  <c:v>2.5649999999999999</c:v>
+                </c:pt>
+                <c:pt idx="2076">
+                  <c:v>2.573</c:v>
+                </c:pt>
+                <c:pt idx="2077">
+                  <c:v>2.5550000000000002</c:v>
+                </c:pt>
+                <c:pt idx="2078">
+                  <c:v>2.5499999999999998</c:v>
+                </c:pt>
+                <c:pt idx="2079">
+                  <c:v>2.5419999999999998</c:v>
+                </c:pt>
+                <c:pt idx="2080">
+                  <c:v>2.5390000000000001</c:v>
+                </c:pt>
+                <c:pt idx="2081">
+                  <c:v>2.5299999999999998</c:v>
+                </c:pt>
+                <c:pt idx="2082">
+                  <c:v>2.5299999999999998</c:v>
+                </c:pt>
+                <c:pt idx="2083">
+                  <c:v>2.54</c:v>
+                </c:pt>
+                <c:pt idx="2084">
+                  <c:v>2.5499999999999998</c:v>
+                </c:pt>
+                <c:pt idx="2085">
+                  <c:v>2.5499999999999998</c:v>
+                </c:pt>
+                <c:pt idx="2086">
+                  <c:v>2.54</c:v>
+                </c:pt>
+                <c:pt idx="2087">
+                  <c:v>2.54</c:v>
+                </c:pt>
+                <c:pt idx="2088">
+                  <c:v>2.5499999999999998</c:v>
+                </c:pt>
+                <c:pt idx="2089">
+                  <c:v>2.5510000000000002</c:v>
+                </c:pt>
+                <c:pt idx="2090">
+                  <c:v>2.6030000000000002</c:v>
+                </c:pt>
+                <c:pt idx="2091">
+                  <c:v>2.54</c:v>
+                </c:pt>
+                <c:pt idx="2092">
+                  <c:v>2.5059999999999998</c:v>
+                </c:pt>
+                <c:pt idx="2093">
+                  <c:v>2.4489999999999998</c:v>
+                </c:pt>
+                <c:pt idx="2094">
+                  <c:v>2.444</c:v>
+                </c:pt>
+                <c:pt idx="2095">
+                  <c:v>2.468</c:v>
+                </c:pt>
+                <c:pt idx="2096">
+                  <c:v>2.4670000000000001</c:v>
+                </c:pt>
+                <c:pt idx="2097">
+                  <c:v>2.5009999999999999</c:v>
+                </c:pt>
+                <c:pt idx="2098">
+                  <c:v>2.5430000000000001</c:v>
+                </c:pt>
+                <c:pt idx="2099">
+                  <c:v>2.56</c:v>
+                </c:pt>
+                <c:pt idx="2100">
+                  <c:v>2.5739999999999998</c:v>
+                </c:pt>
+                <c:pt idx="2101">
+                  <c:v>2.5459999999999998</c:v>
+                </c:pt>
+                <c:pt idx="2102">
+                  <c:v>2.7490000000000001</c:v>
+                </c:pt>
+                <c:pt idx="2103">
+                  <c:v>2.698</c:v>
+                </c:pt>
+                <c:pt idx="2104">
+                  <c:v>2.6789999999999998</c:v>
+                </c:pt>
+                <c:pt idx="2105">
+                  <c:v>2.6760000000000002</c:v>
+                </c:pt>
+                <c:pt idx="2106">
+                  <c:v>2.6680000000000001</c:v>
+                </c:pt>
+                <c:pt idx="2107">
+                  <c:v>2.6720000000000002</c:v>
+                </c:pt>
+                <c:pt idx="2108">
+                  <c:v>2.6819999999999999</c:v>
+                </c:pt>
+                <c:pt idx="2109">
+                  <c:v>2.677</c:v>
+                </c:pt>
+                <c:pt idx="2110">
+                  <c:v>2.6739999999999999</c:v>
+                </c:pt>
+                <c:pt idx="2111">
+                  <c:v>2.706</c:v>
+                </c:pt>
+                <c:pt idx="2112">
+                  <c:v>2.7810000000000001</c:v>
+                </c:pt>
+                <c:pt idx="2113">
+                  <c:v>2.786</c:v>
+                </c:pt>
+                <c:pt idx="2114">
+                  <c:v>2.774</c:v>
+                </c:pt>
+                <c:pt idx="2115">
+                  <c:v>2.7709999999999999</c:v>
+                </c:pt>
+                <c:pt idx="2116">
+                  <c:v>2.754</c:v>
+                </c:pt>
+                <c:pt idx="2117">
+                  <c:v>2.7330000000000001</c:v>
+                </c:pt>
+                <c:pt idx="2118">
+                  <c:v>2.7709999999999999</c:v>
+                </c:pt>
+                <c:pt idx="2119">
+                  <c:v>2.774</c:v>
+                </c:pt>
+                <c:pt idx="2120">
+                  <c:v>2.7850000000000001</c:v>
+                </c:pt>
+                <c:pt idx="2121">
+                  <c:v>2.7679999999999998</c:v>
+                </c:pt>
+                <c:pt idx="2122">
+                  <c:v>2.746</c:v>
+                </c:pt>
+                <c:pt idx="2123">
+                  <c:v>2.738</c:v>
+                </c:pt>
+                <c:pt idx="2124">
+                  <c:v>2.7370000000000001</c:v>
+                </c:pt>
+                <c:pt idx="2125">
+                  <c:v>2.726</c:v>
+                </c:pt>
+                <c:pt idx="2126">
+                  <c:v>2.7269999999999999</c:v>
+                </c:pt>
+                <c:pt idx="2127">
+                  <c:v>2.74</c:v>
+                </c:pt>
+                <c:pt idx="2128">
+                  <c:v>2.74</c:v>
+                </c:pt>
+                <c:pt idx="2129">
+                  <c:v>2.738</c:v>
+                </c:pt>
+                <c:pt idx="2130">
+                  <c:v>2.988</c:v>
+                </c:pt>
+                <c:pt idx="2131">
+                  <c:v>2.99</c:v>
+                </c:pt>
+                <c:pt idx="2132">
+                  <c:v>3.0640000000000001</c:v>
+                </c:pt>
+                <c:pt idx="2133">
+                  <c:v>3.052</c:v>
+                </c:pt>
+                <c:pt idx="2134">
+                  <c:v>2.98</c:v>
+                </c:pt>
+                <c:pt idx="2135">
+                  <c:v>2.948</c:v>
+                </c:pt>
+                <c:pt idx="2136">
+                  <c:v>2.956</c:v>
+                </c:pt>
+                <c:pt idx="2137">
+                  <c:v>2.9910000000000001</c:v>
+                </c:pt>
+                <c:pt idx="2138">
+                  <c:v>3.0830000000000002</c:v>
+                </c:pt>
+                <c:pt idx="2139">
+                  <c:v>3.0830000000000002</c:v>
+                </c:pt>
+                <c:pt idx="2140">
+                  <c:v>3.077</c:v>
+                </c:pt>
+                <c:pt idx="2141">
+                  <c:v>3.0750000000000002</c:v>
+                </c:pt>
+                <c:pt idx="2142">
+                  <c:v>3.0630000000000002</c:v>
+                </c:pt>
+                <c:pt idx="2143">
+                  <c:v>3.05</c:v>
+                </c:pt>
+                <c:pt idx="2144">
+                  <c:v>3.0289999999999999</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -13778,7 +14252,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0DC83E2F-018C-4B5A-96A0-1EEF1FA8E943}">
-  <dimension ref="A1:F2124"/>
+  <dimension ref="A1:F2146"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.83203125" style="9" bestFit="1" customWidth="1"/>
@@ -56262,6 +56736,452 @@
       </c>
       <c r="D2124" s="9" t="s">
         <v>5</v>
+      </c>
+      <c r="E2124" s="11">
+        <v>2.746</v>
+      </c>
+      <c r="F2124" s="12">
+        <v>1195.55423</v>
+      </c>
+    </row>
+    <row r="2125" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A2125" s="9">
+        <v>46252</v>
+      </c>
+      <c r="B2125" s="9">
+        <v>46253</v>
+      </c>
+      <c r="C2125" s="10">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D2125" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2125" s="11">
+        <v>2.738</v>
+      </c>
+      <c r="F2125" s="12">
+        <v>1195.91401</v>
+      </c>
+    </row>
+    <row r="2126" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A2126" s="9">
+        <v>46253</v>
+      </c>
+      <c r="B2126" s="9">
+        <v>46254</v>
+      </c>
+      <c r="C2126" s="10">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D2126" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2126" s="11">
+        <v>2.7370000000000001</v>
+      </c>
+      <c r="F2126" s="12">
+        <v>1196.0037199999999</v>
+      </c>
+    </row>
+    <row r="2127" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A2127" s="9">
+        <v>46254</v>
+      </c>
+      <c r="B2127" s="9">
+        <v>46255</v>
+      </c>
+      <c r="C2127" s="10">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D2127" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2127" s="11">
+        <v>2.726</v>
+      </c>
+      <c r="F2127" s="12">
+        <v>1196.0934</v>
+      </c>
+    </row>
+    <row r="2128" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A2128" s="9">
+        <v>46255</v>
+      </c>
+      <c r="B2128" s="9">
+        <v>46258</v>
+      </c>
+      <c r="C2128" s="10">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D2128" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2128" s="11">
+        <v>2.7269999999999999</v>
+      </c>
+      <c r="F2128" s="12">
+        <v>1196.18273</v>
+      </c>
+    </row>
+    <row r="2129" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A2129" s="9">
+        <v>46258</v>
+      </c>
+      <c r="B2129" s="9">
+        <v>46259</v>
+      </c>
+      <c r="C2129" s="10">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D2129" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2129" s="11">
+        <v>2.74</v>
+      </c>
+      <c r="F2129" s="12">
+        <v>1196.45084</v>
+      </c>
+    </row>
+    <row r="2130" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A2130" s="9">
+        <v>46259</v>
+      </c>
+      <c r="B2130" s="9">
+        <v>46260</v>
+      </c>
+      <c r="C2130" s="10">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D2130" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2130" s="11">
+        <v>2.74</v>
+      </c>
+      <c r="F2130" s="12">
+        <v>1196.5406599999999</v>
+      </c>
+    </row>
+    <row r="2131" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A2131" s="9">
+        <v>46260</v>
+      </c>
+      <c r="B2131" s="9">
+        <v>46261</v>
+      </c>
+      <c r="C2131" s="10">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D2131" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2131" s="11">
+        <v>2.738</v>
+      </c>
+      <c r="F2131" s="12">
+        <v>1196.63048</v>
+      </c>
+    </row>
+    <row r="2132" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A2132" s="9">
+        <v>46261</v>
+      </c>
+      <c r="B2132" s="9">
+        <v>46262</v>
+      </c>
+      <c r="C2132" s="10">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D2132" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2132" s="11">
+        <v>2.988</v>
+      </c>
+      <c r="F2132" s="12">
+        <v>1196.7202400000001</v>
+      </c>
+    </row>
+    <row r="2133" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A2133" s="9">
+        <v>46262</v>
+      </c>
+      <c r="B2133" s="9">
+        <v>46265</v>
+      </c>
+      <c r="C2133" s="10">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D2133" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2133" s="11">
+        <v>2.99</v>
+      </c>
+      <c r="F2133" s="12">
+        <v>1196.8182099999999</v>
+      </c>
+    </row>
+    <row r="2134" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A2134" s="9">
+        <v>46265</v>
+      </c>
+      <c r="B2134" s="9">
+        <v>46266</v>
+      </c>
+      <c r="C2134" s="10">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D2134" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2134" s="11">
+        <v>3.0640000000000001</v>
+      </c>
+      <c r="F2134" s="12">
+        <v>1197.1123299999999</v>
+      </c>
+    </row>
+    <row r="2135" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A2135" s="9">
+        <v>46266</v>
+      </c>
+      <c r="B2135" s="9">
+        <v>46267</v>
+      </c>
+      <c r="C2135" s="10">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D2135" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2135" s="11">
+        <v>3.052</v>
+      </c>
+      <c r="F2135" s="12">
+        <v>1197.21282</v>
+      </c>
+    </row>
+    <row r="2136" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A2136" s="9">
+        <v>46267</v>
+      </c>
+      <c r="B2136" s="9">
+        <v>46268</v>
+      </c>
+      <c r="C2136" s="10">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D2136" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2136" s="11">
+        <v>2.98</v>
+      </c>
+      <c r="F2136" s="12">
+        <v>1197.3129300000001</v>
+      </c>
+    </row>
+    <row r="2137" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A2137" s="9">
+        <v>46268</v>
+      </c>
+      <c r="B2137" s="9">
+        <v>46269</v>
+      </c>
+      <c r="C2137" s="10">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D2137" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2137" s="11">
+        <v>2.948</v>
+      </c>
+      <c r="F2137" s="12">
+        <v>1197.41068</v>
+      </c>
+    </row>
+    <row r="2138" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A2138" s="9">
+        <v>46269</v>
+      </c>
+      <c r="B2138" s="9">
+        <v>46272</v>
+      </c>
+      <c r="C2138" s="10">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D2138" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2138" s="11">
+        <v>2.956</v>
+      </c>
+      <c r="F2138" s="12">
+        <v>1197.50739</v>
+      </c>
+    </row>
+    <row r="2139" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A2139" s="9">
+        <v>46272</v>
+      </c>
+      <c r="B2139" s="9">
+        <v>46273</v>
+      </c>
+      <c r="C2139" s="10">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D2139" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2139" s="11">
+        <v>2.9910000000000001</v>
+      </c>
+      <c r="F2139" s="12">
+        <v>1197.7983400000001</v>
+      </c>
+    </row>
+    <row r="2140" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A2140" s="9">
+        <v>46273</v>
+      </c>
+      <c r="B2140" s="9">
+        <v>46274</v>
+      </c>
+      <c r="C2140" s="10">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D2140" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2140" s="11">
+        <v>3.0830000000000002</v>
+      </c>
+      <c r="F2140" s="12">
+        <v>1197.8964900000001</v>
+      </c>
+    </row>
+    <row r="2141" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A2141" s="9">
+        <v>46274</v>
+      </c>
+      <c r="B2141" s="9">
+        <v>46275</v>
+      </c>
+      <c r="C2141" s="10">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D2141" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2141" s="11">
+        <v>3.0830000000000002</v>
+      </c>
+      <c r="F2141" s="12">
+        <v>1197.99767</v>
+      </c>
+    </row>
+    <row r="2142" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A2142" s="9">
+        <v>46275</v>
+      </c>
+      <c r="B2142" s="9">
+        <v>46276</v>
+      </c>
+      <c r="C2142" s="10">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D2142" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2142" s="11">
+        <v>3.077</v>
+      </c>
+      <c r="F2142" s="12">
+        <v>1198.0988600000001</v>
+      </c>
+    </row>
+    <row r="2143" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A2143" s="9">
+        <v>46276</v>
+      </c>
+      <c r="B2143" s="9">
+        <v>46279</v>
+      </c>
+      <c r="C2143" s="10">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D2143" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2143" s="11">
+        <v>3.0750000000000002</v>
+      </c>
+      <c r="F2143" s="12">
+        <v>1198.1998599999999</v>
+      </c>
+    </row>
+    <row r="2144" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A2144" s="9">
+        <v>46279</v>
+      </c>
+      <c r="B2144" s="9">
+        <v>46280</v>
+      </c>
+      <c r="C2144" s="10">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D2144" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2144" s="11">
+        <v>3.0630000000000002</v>
+      </c>
+      <c r="F2144" s="12">
+        <v>1198.50269</v>
+      </c>
+    </row>
+    <row r="2145" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A2145" s="9">
+        <v>46280</v>
+      </c>
+      <c r="B2145" s="9">
+        <v>46281</v>
+      </c>
+      <c r="C2145" s="10">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D2145" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2145" s="11">
+        <v>3.05</v>
+      </c>
+      <c r="F2145" s="12">
+        <v>1198.6032700000001</v>
+      </c>
+    </row>
+    <row r="2146" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A2146" s="9">
+        <v>46281</v>
+      </c>
+      <c r="B2146" s="9">
+        <v>46283</v>
+      </c>
+      <c r="C2146" s="10">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D2146" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2146" s="11">
+        <v>3.0289999999999999</v>
+      </c>
+      <c r="F2146" s="12">
+        <v>1198.70343</v>
       </c>
     </row>
   </sheetData>
